--- a/artfynd/A 390-2024 artfynd.xlsx
+++ b/artfynd/A 390-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 390-2024 artfynd.xlsx
+++ b/artfynd/A 390-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114123394</v>
+        <v>114985513</v>
       </c>
       <c r="B2" t="n">
-        <v>90201</v>
+        <v>57385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Piteå Kommun, Nb</t>
+          <t>Långmyran, Rosviksbodarna, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810665</v>
+        <v>810605</v>
       </c>
       <c r="R2" t="n">
-        <v>7278560</v>
+        <v>7278439</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 vuxna Talltita, förmodligen 2 hanar och 1 hona, båda hanarna sjunger och ropar, tydligt konkurrensbeteende, parningslek för honorna, honorna födosökande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +782,36 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gammal granskog med många hänglavar, med mycket gamla tallar (&gt;100 år) däremellan och björkar, mycket stående död ved</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Corina Delling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114123392</v>
+        <v>114123394</v>
       </c>
       <c r="B3" t="n">
-        <v>78261</v>
+        <v>90201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +824,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810693</v>
+        <v>810665</v>
       </c>
       <c r="R3" t="n">
-        <v>7278586</v>
+        <v>7278560</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,6 +907,609 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114123392</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78261</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Piteå Kommun, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>810693</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7278586</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114987910</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Rosviksbodarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>810761</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7278442</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stora hackade stycken av bark</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal granskog med massor av hänglavar, med mycket gamla tallar (&gt;100 år) däremellan och björkar, massor av stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114985451</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78474</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmyran, Rosviksbodarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>810784</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7278567</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114986244</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyran, Rosviksbodarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>810633</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7278471</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stora delar av skalad bark på en gran med tydliga larvangrepp</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal granskog med massor av hänglavar, med mycket gamla tallar (&gt;100 år) däremellan och björkar, massor av stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114986863</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmyran, Rosviksbodarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>810644</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7278438</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färskt spår av en svart hackspett, stort yta bark hackat från en gran med larvangrepp</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal granskog med massor av hänglavar, med mycket gamla tallar (&gt;100 år) däremellan och björkar, massor av stående död ved.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
